--- a/public/data/Custos_Auxiliares_Frota_Jan_Abr_2026.xlsx
+++ b/public/data/Custos_Auxiliares_Frota_Jan_Abr_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Área de Trabalho\Fechamentos Transmassa\Projeto_Transmassa\transmassa-apresentacao\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159DBF46-C202-4F72-B3C8-9D9FBAEE2379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE379FD-C51B-42C6-9864-A10F10496077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,7 +471,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -493,6 +493,12 @@
       <sz val="11"/>
       <color rgb="FF243746"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -535,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -549,6 +555,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -559,7 +566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1028,8 +1035,7 @@
   <autoFilter ref="A1:I21" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Pedágio"/>
-        <filter val="Pedágio(Sem Parar)"/>
+        <filter val="Gerenciamento de Riscos"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1240,16 +1246,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="3" t="s">
@@ -1428,58 +1434,58 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="35.1" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" ht="35.1" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" ht="35.1" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" ht="35.1" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1497,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1540,7 +1546,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1569,7 +1575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" hidden="1">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1586,10 +1592,10 @@
         <v>30</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>115518.49</v>
       </c>
       <c r="G3" s="2">
-        <v>1315518.49</v>
+        <v>115518.49</v>
       </c>
       <c r="H3" t="s">
         <v>31</v>
@@ -1615,10 +1621,10 @@
         <v>35</v>
       </c>
       <c r="F4" s="2">
-        <v>516607.52</v>
+        <v>18790.89</v>
       </c>
       <c r="G4" s="2">
-        <v>516607.52</v>
+        <v>18790.89</v>
       </c>
       <c r="H4" t="s">
         <v>36</v>
@@ -1656,7 +1662,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1673,10 +1679,10 @@
         <v>35</v>
       </c>
       <c r="F6" s="2">
-        <v>500491.35</v>
+        <v>26884.99</v>
       </c>
       <c r="G6" s="2">
-        <v>500491.35</v>
+        <v>26884.99</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
@@ -1685,7 +1691,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1714,7 +1720,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1734,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>121500</v>
       </c>
       <c r="H8" t="s">
         <v>31</v>
@@ -1760,10 +1766,10 @@
         <v>35</v>
       </c>
       <c r="F9" s="2">
-        <v>31911.13</v>
+        <v>14403.9</v>
       </c>
       <c r="G9" s="2">
-        <v>31911.13</v>
+        <v>14403.9</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
@@ -1801,7 +1807,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1818,10 +1824,10 @@
         <v>35</v>
       </c>
       <c r="F11" s="2">
-        <v>100079.96</v>
+        <v>31099.21</v>
       </c>
       <c r="G11" s="2">
-        <v>100079.96</v>
+        <v>31099.21</v>
       </c>
       <c r="H11" t="s">
         <v>36</v>
@@ -1830,7 +1836,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" hidden="1">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1859,7 +1865,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" hidden="1">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1879,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2">
-        <v>248399.1</v>
+        <v>126899.1</v>
       </c>
       <c r="H13" t="s">
         <v>31</v>
@@ -1908,7 +1914,7 @@
         <v>31270.959999999999</v>
       </c>
       <c r="G14" s="2">
-        <v>31270.959999999999</v>
+        <v>16445.509999999998</v>
       </c>
       <c r="H14" t="s">
         <v>36</v>
@@ -1946,7 +1952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1963,10 +1969,10 @@
         <v>35</v>
       </c>
       <c r="F16" s="2">
-        <v>81765.75</v>
+        <v>17037.939999999999</v>
       </c>
       <c r="G16" s="2">
-        <v>81765.75</v>
+        <v>17037.939999999999</v>
       </c>
       <c r="H16" t="s">
         <v>36</v>
@@ -1975,7 +1981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" hidden="1">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2004,7 +2010,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" hidden="1">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -2091,7 +2097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -2108,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F21" s="2">
-        <v>103806.45</v>
+        <v>35528.35</v>
       </c>
       <c r="G21" s="2">
-        <v>103806.45</v>
+        <v>35528.35</v>
       </c>
       <c r="H21" t="s">
         <v>36</v>
@@ -2120,32 +2126,33 @@
         <v>37</v>
       </c>
     </row>
+    <row r="25" spans="1:9">
+      <c r="H25" s="12"/>
+    </row>
     <row r="26" spans="1:9">
-      <c r="G26" s="11">
-        <v>121500</v>
-      </c>
-      <c r="I26" s="11">
-        <f>G17-I27</f>
-        <v>-127008.53</v>
-      </c>
+      <c r="G26" s="7"/>
+      <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="G27" s="11">
-        <v>126899.1</v>
-      </c>
-      <c r="I27" s="11">
-        <v>131737.09</v>
-      </c>
+      <c r="G27" s="7"/>
+      <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="G28" s="11"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="G30" s="11"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="G32" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/Custos_Auxiliares_Frota_Jan_Abr_2026.xlsx
+++ b/public/data/Custos_Auxiliares_Frota_Jan_Abr_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Área de Trabalho\Fechamentos Transmassa\Projeto_Transmassa\transmassa-apresentacao\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE379FD-C51B-42C6-9864-A10F10496077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EE235D-7F7F-4DA0-BD87-8893C80F561B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1035,7 +1035,7 @@
   <autoFilter ref="A1:I21" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Gerenciamento de Riscos"/>
+        <filter val="Seguro de Carga"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1604,7 +1604,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" hidden="1">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>33595.43</v>
       </c>
       <c r="G19" s="2">
-        <v>33595.43</v>
+        <v>17037.939999999999</v>
       </c>
       <c r="H19" t="s">
         <v>36</v>
@@ -2097,7 +2097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" t="s">
         <v>15</v>
       </c>
